--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\freight\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FB7481-6E1C-461C-94FE-3245F673C0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4197DD-DEA5-42E8-AD29-ABD0DEF514E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="KCCI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -171,11 +171,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -239,7 +239,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -259,16 +259,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -277,13 +277,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -291,9 +291,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -311,7 +311,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -876,6 +876,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -883,7 +886,7 @@
             <c:numRef>
               <c:f>KCCI!$E$3:$E$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>2892</c:v>
@@ -1397,6 +1400,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>2178</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2186</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1956,6 +1962,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1963,7 +1972,7 @@
             <c:numRef>
               <c:f>KCCI!$F$3:$F$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>1934</c:v>
@@ -2477,6 +2486,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>2467</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2616</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3036,6 +3048,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3043,7 +3058,7 @@
             <c:numRef>
               <c:f>KCCI!$G$3:$G$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>5383</c:v>
@@ -3557,6 +3572,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>3406</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3600</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4116,6 +4134,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4123,7 +4144,7 @@
             <c:numRef>
               <c:f>KCCI!$H$3:$H$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>4016</c:v>
@@ -4637,6 +4658,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>2646</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2534</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5196,6 +5220,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5203,7 +5230,7 @@
             <c:numRef>
               <c:f>KCCI!$I$3:$I$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>4475</c:v>
@@ -5717,6 +5744,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>3730</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3574</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6276,6 +6306,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6283,7 +6316,7 @@
             <c:numRef>
               <c:f>KCCI!$J$3:$J$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>3359</c:v>
@@ -6797,6 +6830,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>6211</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>6249</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7358,6 +7394,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7365,7 +7404,7 @@
             <c:numRef>
               <c:f>KCCI!$K$3:$K$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>4166</c:v>
@@ -7879,6 +7918,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>1509</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8440,6 +8482,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8447,7 +8492,7 @@
             <c:numRef>
               <c:f>KCCI!$L$3:$L$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>5075</c:v>
@@ -8961,6 +9006,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>3148</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3068</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9522,6 +9570,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9529,7 +9580,7 @@
             <c:numRef>
               <c:f>KCCI!$M$3:$M$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>3854</c:v>
@@ -10043,6 +10094,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>3089</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10604,6 +10658,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10611,7 +10668,7 @@
             <c:numRef>
               <c:f>KCCI!$N$3:$N$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>6459</c:v>
@@ -11125,6 +11182,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>2984</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2874</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11686,6 +11746,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11693,7 +11756,7 @@
             <c:numRef>
               <c:f>KCCI!$O$3:$O$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>6028</c:v>
@@ -12207,6 +12270,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>4068</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>4042</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12784,6 +12850,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12791,7 +12860,7 @@
             <c:numRef>
               <c:f>KCCI!$P$3:$P$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>295</c:v>
@@ -13304,6 +13373,9 @@
                   <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="170">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="171">
                   <c:v>59</c:v>
                 </c:pt>
               </c:numCache>
@@ -13867,6 +13939,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13874,7 +13949,7 @@
             <c:numRef>
               <c:f>KCCI!$Q$3:$Q$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>881</c:v>
@@ -14388,6 +14463,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>246</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>245</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14950,6 +15028,9 @@
                 <c:pt idx="170">
                   <c:v>46118</c:v>
                 </c:pt>
+                <c:pt idx="171">
+                  <c:v>46125</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14957,7 +15038,7 @@
             <c:numRef>
               <c:f>KCCI!$R$3:$R$11166</c:f>
               <c:numCache>
-                <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"_-;_-@_-</c:formatCode>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
                 <c:ptCount val="11164"/>
                 <c:pt idx="0">
                   <c:v>1708</c:v>
@@ -15471,6 +15552,9 @@
                 </c:pt>
                 <c:pt idx="170">
                   <c:v>1070</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1085</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15570,7 +15654,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -15612,7 +15696,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
-        <c:numFmt formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -16342,9 +16426,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -16382,7 +16466,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -16488,7 +16572,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -16630,7 +16714,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -16638,19 +16722,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S173"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
+  <dimension ref="A1:S174"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" style="3" customWidth="1"/>
-    <col min="5" max="18" width="12.81640625" style="7" customWidth="1"/>
-    <col min="19" max="19" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" style="3" customWidth="1"/>
+    <col min="5" max="18" width="12.77734375" style="7" customWidth="1"/>
+    <col min="19" max="19" width="11.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>14</v>
       </c>
@@ -16706,7 +16790,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="12"/>
@@ -16754,7 +16838,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>44872</v>
       </c>
@@ -16811,7 +16895,7 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>44879</v>
       </c>
@@ -16868,7 +16952,7 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>44886</v>
       </c>
@@ -16925,7 +17009,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>44893</v>
       </c>
@@ -16982,7 +17066,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>44900</v>
       </c>
@@ -17039,7 +17123,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>44907</v>
       </c>
@@ -17096,7 +17180,7 @@
       </c>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>44914</v>
       </c>
@@ -17153,7 +17237,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>44921</v>
       </c>
@@ -17210,7 +17294,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>44928</v>
       </c>
@@ -17267,7 +17351,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>44935</v>
       </c>
@@ -17324,7 +17408,7 @@
       </c>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>44942</v>
       </c>
@@ -17381,7 +17465,7 @@
       </c>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>44951</v>
       </c>
@@ -17438,7 +17522,7 @@
       </c>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>44956</v>
       </c>
@@ -17495,7 +17579,7 @@
       </c>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>44963</v>
       </c>
@@ -17552,7 +17636,7 @@
       </c>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>44970</v>
       </c>
@@ -17609,7 +17693,7 @@
       </c>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>44977</v>
       </c>
@@ -17666,7 +17750,7 @@
       </c>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>44984</v>
       </c>
@@ -17723,7 +17807,7 @@
       </c>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>44991</v>
       </c>
@@ -17780,7 +17864,7 @@
       </c>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>44998</v>
       </c>
@@ -17837,7 +17921,7 @@
       </c>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>45005</v>
       </c>
@@ -17894,7 +17978,7 @@
       </c>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>45012</v>
       </c>
@@ -17951,7 +18035,7 @@
       </c>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>45019</v>
       </c>
@@ -18008,7 +18092,7 @@
       </c>
       <c r="S24" s="1"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>45026</v>
       </c>
@@ -18065,7 +18149,7 @@
       </c>
       <c r="S25" s="1"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>45033</v>
       </c>
@@ -18122,7 +18206,7 @@
       </c>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>45040</v>
       </c>
@@ -18179,7 +18263,7 @@
       </c>
       <c r="S27" s="1"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>45048</v>
       </c>
@@ -18236,7 +18320,7 @@
       </c>
       <c r="S28" s="1"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>45054</v>
       </c>
@@ -18293,7 +18377,7 @@
       </c>
       <c r="S29" s="1"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>45061</v>
       </c>
@@ -18350,7 +18434,7 @@
       </c>
       <c r="S30" s="1"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>45068</v>
       </c>
@@ -18407,7 +18491,7 @@
       </c>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>45076</v>
       </c>
@@ -18464,7 +18548,7 @@
       </c>
       <c r="S32" s="1"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>45082</v>
       </c>
@@ -18521,7 +18605,7 @@
       </c>
       <c r="S33" s="1"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>45089</v>
       </c>
@@ -18578,7 +18662,7 @@
       </c>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>45096</v>
       </c>
@@ -18635,7 +18719,7 @@
       </c>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>45103</v>
       </c>
@@ -18692,7 +18776,7 @@
       </c>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>45110</v>
       </c>
@@ -18749,7 +18833,7 @@
       </c>
       <c r="S37" s="1"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>45117</v>
       </c>
@@ -18806,7 +18890,7 @@
       </c>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>45124</v>
       </c>
@@ -18863,7 +18947,7 @@
       </c>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>45131</v>
       </c>
@@ -18920,7 +19004,7 @@
       </c>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>45138</v>
       </c>
@@ -18977,7 +19061,7 @@
       </c>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>45145</v>
       </c>
@@ -19034,7 +19118,7 @@
       </c>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>45152</v>
       </c>
@@ -19091,7 +19175,7 @@
       </c>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>45159</v>
       </c>
@@ -19148,7 +19232,7 @@
       </c>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>45166</v>
       </c>
@@ -19205,7 +19289,7 @@
       </c>
       <c r="S45" s="1"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>45173</v>
       </c>
@@ -19262,7 +19346,7 @@
       </c>
       <c r="S46" s="1"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>45180</v>
       </c>
@@ -19319,7 +19403,7 @@
       </c>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>45187</v>
       </c>
@@ -19376,7 +19460,7 @@
       </c>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="10">
         <v>45194</v>
       </c>
@@ -19433,7 +19517,7 @@
       </c>
       <c r="S49" s="1"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" s="10">
         <v>45209</v>
       </c>
@@ -19490,7 +19574,7 @@
       </c>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="10">
         <v>45215</v>
       </c>
@@ -19547,7 +19631,7 @@
       </c>
       <c r="S51" s="1"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" s="10">
         <v>45222</v>
       </c>
@@ -19604,7 +19688,7 @@
       </c>
       <c r="S52" s="1"/>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>45229</v>
       </c>
@@ -19661,7 +19745,7 @@
       </c>
       <c r="S53" s="1"/>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" s="10">
         <v>45236</v>
       </c>
@@ -19718,7 +19802,7 @@
       </c>
       <c r="S54" s="1"/>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" s="10">
         <v>45243</v>
       </c>
@@ -19775,7 +19859,7 @@
       </c>
       <c r="S55" s="1"/>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" s="10">
         <v>45250</v>
       </c>
@@ -19832,7 +19916,7 @@
       </c>
       <c r="S56" s="1"/>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" s="10">
         <v>45257</v>
       </c>
@@ -19889,7 +19973,7 @@
       </c>
       <c r="S57" s="1"/>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" s="10">
         <v>45264</v>
       </c>
@@ -19946,7 +20030,7 @@
       </c>
       <c r="S58" s="1"/>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="10">
         <v>45271</v>
       </c>
@@ -20003,7 +20087,7 @@
       </c>
       <c r="S59" s="1"/>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="10">
         <v>45278</v>
       </c>
@@ -20060,7 +20144,7 @@
       </c>
       <c r="S60" s="1"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="10">
         <v>45286</v>
       </c>
@@ -20117,7 +20201,7 @@
       </c>
       <c r="S61" s="1"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="10">
         <v>45293</v>
       </c>
@@ -20174,7 +20258,7 @@
       </c>
       <c r="S62" s="1"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="10">
         <v>45299</v>
       </c>
@@ -20231,7 +20315,7 @@
       </c>
       <c r="S63" s="1"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="10">
         <v>45306</v>
       </c>
@@ -20288,7 +20372,7 @@
       </c>
       <c r="S64" s="1"/>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="10">
         <v>45313</v>
       </c>
@@ -20345,7 +20429,7 @@
       </c>
       <c r="S65" s="1"/>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="10">
         <v>45320</v>
       </c>
@@ -20402,7 +20486,7 @@
       </c>
       <c r="S66" s="1"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="10">
         <v>45327</v>
       </c>
@@ -20459,7 +20543,7 @@
       </c>
       <c r="S67" s="1"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="10">
         <v>45335</v>
       </c>
@@ -20516,7 +20600,7 @@
       </c>
       <c r="S68" s="1"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="10">
         <v>45341</v>
       </c>
@@ -20573,7 +20657,7 @@
       </c>
       <c r="S69" s="1"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="10">
         <v>45348</v>
       </c>
@@ -20630,7 +20714,7 @@
       </c>
       <c r="S70" s="1"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="10">
         <v>45355</v>
       </c>
@@ -20687,7 +20771,7 @@
       </c>
       <c r="S71" s="1"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="10">
         <v>45362</v>
       </c>
@@ -20744,7 +20828,7 @@
       </c>
       <c r="S72" s="1"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" s="10">
         <v>45369</v>
       </c>
@@ -20801,7 +20885,7 @@
       </c>
       <c r="S73" s="1"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="10">
         <v>45376</v>
       </c>
@@ -20858,7 +20942,7 @@
       </c>
       <c r="S74" s="1"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="10">
         <v>45383</v>
       </c>
@@ -20915,7 +20999,7 @@
       </c>
       <c r="S75" s="1"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="10">
         <v>45390</v>
       </c>
@@ -20972,7 +21056,7 @@
       </c>
       <c r="S76" s="1"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="10">
         <v>45397</v>
       </c>
@@ -21029,7 +21113,7 @@
       </c>
       <c r="S77" s="1"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="10">
         <v>45404</v>
       </c>
@@ -21086,7 +21170,7 @@
       </c>
       <c r="S78" s="1"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="10">
         <v>45411</v>
       </c>
@@ -21143,7 +21227,7 @@
       </c>
       <c r="S79" s="1"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" s="10">
         <v>45419</v>
       </c>
@@ -21200,7 +21284,7 @@
       </c>
       <c r="S80" s="1"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" s="10">
         <v>45425</v>
       </c>
@@ -21257,7 +21341,7 @@
       </c>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" s="10">
         <v>45432</v>
       </c>
@@ -21314,7 +21398,7 @@
       </c>
       <c r="S82" s="1"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" s="10">
         <v>45439</v>
       </c>
@@ -21371,7 +21455,7 @@
       </c>
       <c r="S83" s="1"/>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" s="10">
         <v>45446</v>
       </c>
@@ -21428,7 +21512,7 @@
       </c>
       <c r="S84" s="1"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" s="10">
         <v>45453</v>
       </c>
@@ -21485,7 +21569,7 @@
       </c>
       <c r="S85" s="1"/>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" s="10">
         <v>45460</v>
       </c>
@@ -21542,7 +21626,7 @@
       </c>
       <c r="S86" s="1"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" s="10">
         <v>45467</v>
       </c>
@@ -21599,7 +21683,7 @@
       </c>
       <c r="S87" s="1"/>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" s="10">
         <v>45474</v>
       </c>
@@ -21656,7 +21740,7 @@
       </c>
       <c r="S88" s="1"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" s="10">
         <v>45481</v>
       </c>
@@ -21713,7 +21797,7 @@
       </c>
       <c r="S89" s="1"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" s="10">
         <v>45488</v>
       </c>
@@ -21770,7 +21854,7 @@
       </c>
       <c r="S90" s="1"/>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" s="10">
         <v>45495</v>
       </c>
@@ -21827,7 +21911,7 @@
       </c>
       <c r="S91" s="1"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" s="10">
         <v>45502</v>
       </c>
@@ -21884,7 +21968,7 @@
       </c>
       <c r="S92" s="1"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" s="10">
         <v>45509</v>
       </c>
@@ -21941,7 +22025,7 @@
       </c>
       <c r="S93" s="1"/>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" s="10">
         <v>45516</v>
       </c>
@@ -21998,7 +22082,7 @@
       </c>
       <c r="S94" s="1"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" s="10">
         <v>45523</v>
       </c>
@@ -22055,7 +22139,7 @@
       </c>
       <c r="S95" s="1"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" s="10">
         <v>45530</v>
       </c>
@@ -22112,7 +22196,7 @@
       </c>
       <c r="S96" s="1"/>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" s="10">
         <v>45537</v>
       </c>
@@ -22169,7 +22253,7 @@
       </c>
       <c r="S97" s="1"/>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" s="10">
         <v>45544</v>
       </c>
@@ -22226,7 +22310,7 @@
       </c>
       <c r="S98" s="1"/>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" s="10">
         <v>45558</v>
       </c>
@@ -22283,7 +22367,7 @@
       </c>
       <c r="S99" s="1"/>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" s="10">
         <v>45565</v>
       </c>
@@ -22340,7 +22424,7 @@
       </c>
       <c r="S100" s="1"/>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" s="10">
         <v>45572</v>
       </c>
@@ -22397,7 +22481,7 @@
       </c>
       <c r="S101" s="1"/>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" s="10">
         <v>45579</v>
       </c>
@@ -22454,7 +22538,7 @@
       </c>
       <c r="S102" s="1"/>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" s="10">
         <v>45586</v>
       </c>
@@ -22511,7 +22595,7 @@
       </c>
       <c r="S103" s="1"/>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" s="10">
         <v>45593</v>
       </c>
@@ -22568,7 +22652,7 @@
       </c>
       <c r="S104" s="1"/>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" s="10">
         <v>45600</v>
       </c>
@@ -22625,7 +22709,7 @@
       </c>
       <c r="S105" s="1"/>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" s="10">
         <v>45607</v>
       </c>
@@ -22682,7 +22766,7 @@
       </c>
       <c r="S106" s="1"/>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" s="10">
         <v>45614</v>
       </c>
@@ -22739,7 +22823,7 @@
       </c>
       <c r="S107" s="1"/>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" s="10">
         <v>45621</v>
       </c>
@@ -22796,7 +22880,7 @@
       </c>
       <c r="S108" s="1"/>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" s="10">
         <v>45628</v>
       </c>
@@ -22853,7 +22937,7 @@
       </c>
       <c r="S109" s="1"/>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" s="10">
         <v>45635</v>
       </c>
@@ -22910,7 +22994,7 @@
       </c>
       <c r="S110" s="1"/>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" s="10">
         <v>45642</v>
       </c>
@@ -22967,7 +23051,7 @@
       </c>
       <c r="S111" s="1"/>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" s="10">
         <v>45649</v>
       </c>
@@ -23024,7 +23108,7 @@
       </c>
       <c r="S112" s="1"/>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" s="10">
         <v>45656</v>
       </c>
@@ -23081,7 +23165,7 @@
       </c>
       <c r="S113" s="1"/>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" s="10">
         <v>45663</v>
       </c>
@@ -23138,7 +23222,7 @@
       </c>
       <c r="S114" s="1"/>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" s="10">
         <v>45670</v>
       </c>
@@ -23195,7 +23279,7 @@
       </c>
       <c r="S115" s="1"/>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" s="10">
         <v>45677</v>
       </c>
@@ -23252,7 +23336,7 @@
       </c>
       <c r="S116" s="1"/>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" s="10">
         <v>45691</v>
       </c>
@@ -23309,7 +23393,7 @@
       </c>
       <c r="S117" s="1"/>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" s="10">
         <v>45698</v>
       </c>
@@ -23366,7 +23450,7 @@
       </c>
       <c r="S118" s="1"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" s="10">
         <v>45705</v>
       </c>
@@ -23423,7 +23507,7 @@
       </c>
       <c r="S119" s="1"/>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" s="10">
         <v>45712</v>
       </c>
@@ -23480,7 +23564,7 @@
       </c>
       <c r="S120" s="1"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" s="10">
         <v>45720</v>
       </c>
@@ -23537,7 +23621,7 @@
       </c>
       <c r="S121" s="1"/>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" s="10">
         <v>45726</v>
       </c>
@@ -23594,7 +23678,7 @@
       </c>
       <c r="S122" s="1"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" s="10">
         <v>45733</v>
       </c>
@@ -23651,7 +23735,7 @@
       </c>
       <c r="S123" s="1"/>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124" s="10">
         <v>45740</v>
       </c>
@@ -23708,7 +23792,7 @@
       </c>
       <c r="S124" s="1"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" s="10">
         <v>45747</v>
       </c>
@@ -23765,7 +23849,7 @@
       </c>
       <c r="S125" s="1"/>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" s="10">
         <v>45754</v>
       </c>
@@ -23822,7 +23906,7 @@
       </c>
       <c r="S126" s="1"/>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127" s="10">
         <v>45761</v>
       </c>
@@ -23879,7 +23963,7 @@
       </c>
       <c r="S127" s="1"/>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128" s="10">
         <v>45768</v>
       </c>
@@ -23936,7 +24020,7 @@
       </c>
       <c r="S128" s="1"/>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" s="10">
         <v>45775</v>
       </c>
@@ -23993,7 +24077,7 @@
       </c>
       <c r="S129" s="1"/>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" s="10">
         <v>45789</v>
       </c>
@@ -24050,7 +24134,7 @@
       </c>
       <c r="S130" s="1"/>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" s="10">
         <v>45796</v>
       </c>
@@ -24107,7 +24191,7 @@
       </c>
       <c r="S131" s="1"/>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" s="10">
         <v>45803</v>
       </c>
@@ -24164,7 +24248,7 @@
       </c>
       <c r="S132" s="1"/>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" s="10">
         <v>45810</v>
       </c>
@@ -24221,7 +24305,7 @@
       </c>
       <c r="S133" s="1"/>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" s="10">
         <v>45817</v>
       </c>
@@ -24278,7 +24362,7 @@
       </c>
       <c r="S134" s="1"/>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" s="10">
         <v>45824</v>
       </c>
@@ -24335,7 +24419,7 @@
       </c>
       <c r="S135" s="1"/>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" s="10">
         <v>45831</v>
       </c>
@@ -24392,7 +24476,7 @@
       </c>
       <c r="S136" s="1"/>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" s="10">
         <v>45838</v>
       </c>
@@ -24449,7 +24533,7 @@
       </c>
       <c r="S137" s="1"/>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" s="10">
         <v>45845</v>
       </c>
@@ -24506,7 +24590,7 @@
       </c>
       <c r="S138" s="1"/>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" s="10">
         <v>45852</v>
       </c>
@@ -24563,7 +24647,7 @@
       </c>
       <c r="S139" s="1"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" s="10">
         <v>45859</v>
       </c>
@@ -24620,7 +24704,7 @@
       </c>
       <c r="S140" s="1"/>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" s="10">
         <v>45866</v>
       </c>
@@ -24677,7 +24761,7 @@
       </c>
       <c r="S141" s="1"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142" s="10">
         <v>45873</v>
       </c>
@@ -24734,7 +24818,7 @@
       </c>
       <c r="S142" s="1"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" s="10">
         <v>45880</v>
       </c>
@@ -24791,7 +24875,7 @@
       </c>
       <c r="S143" s="1"/>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144" s="10">
         <v>45887</v>
       </c>
@@ -24848,7 +24932,7 @@
       </c>
       <c r="S144" s="1"/>
     </row>
-    <row r="145" spans="1:19">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145" s="10">
         <v>45894</v>
       </c>
@@ -24905,7 +24989,7 @@
       </c>
       <c r="S145" s="1"/>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146" s="10">
         <v>45901</v>
       </c>
@@ -24962,7 +25046,7 @@
       </c>
       <c r="S146" s="1"/>
     </row>
-    <row r="147" spans="1:19">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147" s="10">
         <v>45908</v>
       </c>
@@ -25019,7 +25103,7 @@
       </c>
       <c r="S147" s="1"/>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148" s="10">
         <v>45915</v>
       </c>
@@ -25076,7 +25160,7 @@
       </c>
       <c r="S148" s="1"/>
     </row>
-    <row r="149" spans="1:19">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149" s="10">
         <v>45922</v>
       </c>
@@ -25133,7 +25217,7 @@
       </c>
       <c r="S149" s="1"/>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150" s="10">
         <v>45929</v>
       </c>
@@ -25190,7 +25274,7 @@
       </c>
       <c r="S150" s="1"/>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151" s="10">
         <v>45950</v>
       </c>
@@ -25247,7 +25331,7 @@
       </c>
       <c r="S151" s="1"/>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152" s="10">
         <v>45957</v>
       </c>
@@ -25304,7 +25388,7 @@
       </c>
       <c r="S152" s="1"/>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153" s="10">
         <v>45964</v>
       </c>
@@ -25361,7 +25445,7 @@
       </c>
       <c r="S153" s="1"/>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154" s="10">
         <v>45971</v>
       </c>
@@ -25418,7 +25502,7 @@
       </c>
       <c r="S154" s="1"/>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155" s="10">
         <v>45978</v>
       </c>
@@ -25475,7 +25559,7 @@
       </c>
       <c r="S155" s="1"/>
     </row>
-    <row r="156" spans="1:19">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156" s="10">
         <v>45985</v>
       </c>
@@ -25532,7 +25616,7 @@
       </c>
       <c r="S156" s="1"/>
     </row>
-    <row r="157" spans="1:19">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157" s="10">
         <v>45992</v>
       </c>
@@ -25589,7 +25673,7 @@
       </c>
       <c r="S157" s="1"/>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158" s="10">
         <v>45999</v>
       </c>
@@ -25646,7 +25730,7 @@
       </c>
       <c r="S158" s="1"/>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A159" s="10">
         <v>46006</v>
       </c>
@@ -25703,7 +25787,7 @@
       </c>
       <c r="S159" s="1"/>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160" s="10">
         <v>46013</v>
       </c>
@@ -25760,7 +25844,7 @@
       </c>
       <c r="S160" s="1"/>
     </row>
-    <row r="161" spans="1:19">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161" s="10">
         <v>46020</v>
       </c>
@@ -25817,7 +25901,7 @@
       </c>
       <c r="S161" s="1"/>
     </row>
-    <row r="162" spans="1:19">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A162" s="10">
         <v>46034</v>
       </c>
@@ -25874,7 +25958,7 @@
       </c>
       <c r="S162" s="1"/>
     </row>
-    <row r="163" spans="1:19">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A163" s="10">
         <v>46041</v>
       </c>
@@ -25931,7 +26015,7 @@
       </c>
       <c r="S163" s="1"/>
     </row>
-    <row r="164" spans="1:19">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A164" s="10">
         <v>46048</v>
       </c>
@@ -25988,7 +26072,7 @@
       </c>
       <c r="S164" s="1"/>
     </row>
-    <row r="165" spans="1:19">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A165" s="10">
         <v>46055</v>
       </c>
@@ -26045,7 +26129,7 @@
       </c>
       <c r="S165" s="1"/>
     </row>
-    <row r="166" spans="1:19">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A166" s="10">
         <v>46062</v>
       </c>
@@ -26102,7 +26186,7 @@
       </c>
       <c r="S166" s="1"/>
     </row>
-    <row r="167" spans="1:19">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A167" s="10">
         <v>46076</v>
       </c>
@@ -26158,7 +26242,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="168" spans="1:19">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A168" s="10">
         <v>46084</v>
       </c>
@@ -26214,7 +26298,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="169" spans="1:19">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A169" s="10">
         <v>46090</v>
       </c>
@@ -26270,7 +26354,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="170" spans="1:19">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A170" s="10">
         <v>46097</v>
       </c>
@@ -26326,7 +26410,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="171" spans="1:19">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A171" s="10">
         <v>46104</v>
       </c>
@@ -26382,7 +26466,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="172" spans="1:19">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A172" s="10">
         <v>46111</v>
       </c>
@@ -26438,7 +26522,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="173" spans="1:19">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A173" s="10">
         <v>46118</v>
       </c>
@@ -26492,6 +26576,62 @@
       </c>
       <c r="R173" s="7">
         <v>1070</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A174" s="10">
+        <v>46125</v>
+      </c>
+      <c r="B174" s="10">
+        <v>46125</v>
+      </c>
+      <c r="C174" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E174" s="7">
+        <v>2186</v>
+      </c>
+      <c r="F174" s="7">
+        <v>2616</v>
+      </c>
+      <c r="G174" s="7">
+        <v>3600</v>
+      </c>
+      <c r="H174" s="7">
+        <v>2534</v>
+      </c>
+      <c r="I174" s="7">
+        <v>3574</v>
+      </c>
+      <c r="J174" s="7">
+        <v>6249</v>
+      </c>
+      <c r="K174" s="7">
+        <v>1502</v>
+      </c>
+      <c r="L174" s="7">
+        <v>3068</v>
+      </c>
+      <c r="M174" s="7">
+        <v>2959</v>
+      </c>
+      <c r="N174" s="7">
+        <v>2874</v>
+      </c>
+      <c r="O174" s="7">
+        <v>4042</v>
+      </c>
+      <c r="P174" s="7">
+        <v>59</v>
+      </c>
+      <c r="Q174" s="7">
+        <v>245</v>
+      </c>
+      <c r="R174" s="7">
+        <v>1085</v>
       </c>
     </row>
   </sheetData>
@@ -26513,14 +26653,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EF7E42-3273-4C27-80E3-741AD2FB330F}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="2"/>
-    <col min="2" max="2" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="9.21875" style="2"/>
+    <col min="2" max="2" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="16">
+    <row r="2" spans="2:3" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
@@ -26528,7 +26668,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="8" t="s">
         <v>34</v>
       </c>
@@ -26549,9 +26689,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BD5038-94A8-4C07-9E87-4FDF24EEDBD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94A7A7BF-7EDB-4568-9B7D-D7F75A1EE6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168AFC5F-D800-4592-9BB9-0EF134C458C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -359,10 +359,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -884,16 +884,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$E$3:$E$11166</c:f>
+              <c:f>KCCI!$E$3:$E$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>2892</c:v>
                 </c:pt>
@@ -1415,6 +1418,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>2192</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>2194</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,10 +1463,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -1982,16 +1988,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$F$3:$F$11166</c:f>
+              <c:f>KCCI!$F$3:$F$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1934</c:v>
                 </c:pt>
@@ -2513,6 +2522,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>2752</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>2753</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2555,10 +2567,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -3080,16 +3092,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$G$3:$G$11166</c:f>
+              <c:f>KCCI!$G$3:$G$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5383</c:v>
                 </c:pt>
@@ -3611,6 +3626,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>3743</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3787</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3653,10 +3671,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -4178,16 +4196,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$H$3:$H$11166</c:f>
+              <c:f>KCCI!$H$3:$H$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4016</c:v>
                 </c:pt>
@@ -4709,6 +4730,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>2377</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>2353</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4751,10 +4775,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -5276,16 +5300,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$I$3:$I$11166</c:f>
+              <c:f>KCCI!$I$3:$I$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4475</c:v>
                 </c:pt>
@@ -5807,6 +5834,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>3460</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3415</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5849,10 +5879,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -6374,16 +6404,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$J$3:$J$11166</c:f>
+              <c:f>KCCI!$J$3:$J$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3359</c:v>
                 </c:pt>
@@ -6905,6 +6938,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>6147</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5939</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6949,10 +6985,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -7474,16 +7510,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$K$3:$K$11166</c:f>
+              <c:f>KCCI!$K$3:$K$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>4166</c:v>
                 </c:pt>
@@ -8005,6 +8044,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>1691</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8049,10 +8091,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -8574,16 +8616,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$L$3:$L$11166</c:f>
+              <c:f>KCCI!$L$3:$L$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>5075</c:v>
                 </c:pt>
@@ -9105,6 +9150,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>2854</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3007</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9149,10 +9197,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -9674,16 +9722,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$M$3:$M$11166</c:f>
+              <c:f>KCCI!$M$3:$M$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>3854</c:v>
                 </c:pt>
@@ -10205,6 +10256,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>2785</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>2742</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10249,10 +10303,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -10774,16 +10828,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$N$3:$N$11166</c:f>
+              <c:f>KCCI!$N$3:$N$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6459</c:v>
                 </c:pt>
@@ -11305,6 +11362,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>2911</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3177</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11349,10 +11409,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -11874,16 +11934,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$O$3:$O$11166</c:f>
+              <c:f>KCCI!$O$3:$O$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>6028</c:v>
                 </c:pt>
@@ -12405,6 +12468,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>4149</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4251</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12465,10 +12531,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -12990,16 +13056,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$P$3:$P$11166</c:f>
+              <c:f>KCCI!$P$3:$P$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>295</c:v>
                 </c:pt>
@@ -13520,6 +13589,9 @@
                   <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="173">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="174">
                   <c:v>56</c:v>
                 </c:pt>
               </c:numCache>
@@ -13566,10 +13638,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -14091,16 +14163,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$Q$3:$Q$11166</c:f>
+              <c:f>KCCI!$Q$3:$Q$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>881</c:v>
                 </c:pt>
@@ -14621,6 +14696,9 @@
                   <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="173">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="174">
                   <c:v>245</c:v>
                 </c:pt>
               </c:numCache>
@@ -14667,10 +14745,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>KCCI!$B$3:$B$11166</c:f>
+              <c:f>KCCI!$B$3:$B$11165</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>44872</c:v>
                 </c:pt>
@@ -15192,16 +15270,19 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>46139</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>46153</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>KCCI!$R$3:$R$11166</c:f>
+              <c:f>KCCI!$R$3:$R$11165</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
-                <c:ptCount val="11164"/>
+                <c:ptCount val="11163"/>
                 <c:pt idx="0">
                   <c:v>1708</c:v>
                 </c:pt>
@@ -15723,6 +15804,9 @@
                 </c:pt>
                 <c:pt idx="173">
                   <c:v>1097</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1077</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16890,7 +16974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S176"/>
+  <dimension ref="A1:S177"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
@@ -26912,6 +26996,62 @@
       </c>
       <c r="R176" s="7">
         <v>1097</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A177" s="10">
+        <v>46153</v>
+      </c>
+      <c r="B177" s="10">
+        <v>46153</v>
+      </c>
+      <c r="C177" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E177" s="7">
+        <v>2194</v>
+      </c>
+      <c r="F177" s="7">
+        <v>2753</v>
+      </c>
+      <c r="G177" s="7">
+        <v>3787</v>
+      </c>
+      <c r="H177" s="7">
+        <v>2353</v>
+      </c>
+      <c r="I177" s="7">
+        <v>3415</v>
+      </c>
+      <c r="J177" s="7">
+        <v>5939</v>
+      </c>
+      <c r="K177" s="7">
+        <v>1729</v>
+      </c>
+      <c r="L177" s="7">
+        <v>3007</v>
+      </c>
+      <c r="M177" s="7">
+        <v>2742</v>
+      </c>
+      <c r="N177" s="7">
+        <v>3177</v>
+      </c>
+      <c r="O177" s="7">
+        <v>4251</v>
+      </c>
+      <c r="P177" s="7">
+        <v>56</v>
+      </c>
+      <c r="Q177" s="7">
+        <v>245</v>
+      </c>
+      <c r="R177" s="7">
+        <v>1077</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478CE8CD-7BD9-4E57-BDED-083FDC00AE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD61F9D6-EE98-4B02-8A86-9BED797F2242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="38">
   <si>
     <t>KCCI</t>
   </si>
@@ -899,6 +899,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1435,6 +1438,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>2361</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>2478</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2009,6 +2015,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2545,6 +2554,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>3011</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3135</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3119,6 +3131,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3655,6 +3670,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>4103</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4257</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4229,6 +4247,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4765,6 +4786,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>2679</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>2838</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5339,6 +5363,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5875,6 +5902,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>3866</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4133</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6449,6 +6479,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6985,6 +7018,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>5934</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7561,6 +7597,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8097,6 +8136,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>1864</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>2013</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8673,6 +8715,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9209,6 +9254,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>3484</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3967</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9785,6 +9833,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10321,6 +10372,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>3054</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3340</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10897,6 +10951,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11433,6 +11490,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>3035</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3060</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12009,6 +12069,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12545,6 +12608,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>4250</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4326</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13137,6 +13203,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13673,6 +13742,9 @@
                 </c:pt>
                 <c:pt idx="175">
                   <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14250,6 +14322,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14785,6 +14860,9 @@
                   <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="175">
+                  <c:v>238</c:v>
+                </c:pt>
+                <c:pt idx="176">
                   <c:v>238</c:v>
                 </c:pt>
               </c:numCache>
@@ -15363,6 +15441,9 @@
                 <c:pt idx="175">
                   <c:v>46160</c:v>
                 </c:pt>
+                <c:pt idx="176">
+                  <c:v>46168</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15898,6 +15979,9 @@
                   <c:v>1077</c:v>
                 </c:pt>
                 <c:pt idx="175">
+                  <c:v>1075</c:v>
+                </c:pt>
+                <c:pt idx="176">
                   <c:v>1075</c:v>
                 </c:pt>
               </c:numCache>
@@ -17066,7 +17150,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S178"/>
+  <dimension ref="A1:S179"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="10" bestFit="1" customWidth="1"/>
@@ -27199,6 +27283,62 @@
         <v>238</v>
       </c>
       <c r="R178" s="7">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A179" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B179" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C179" s="4">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E179" s="7">
+        <v>2478</v>
+      </c>
+      <c r="F179" s="7">
+        <v>3135</v>
+      </c>
+      <c r="G179" s="7">
+        <v>4257</v>
+      </c>
+      <c r="H179" s="7">
+        <v>2838</v>
+      </c>
+      <c r="I179" s="7">
+        <v>4133</v>
+      </c>
+      <c r="J179" s="7">
+        <v>5991</v>
+      </c>
+      <c r="K179" s="7">
+        <v>2013</v>
+      </c>
+      <c r="L179" s="7">
+        <v>3967</v>
+      </c>
+      <c r="M179" s="7">
+        <v>3340</v>
+      </c>
+      <c r="N179" s="7">
+        <v>3060</v>
+      </c>
+      <c r="O179" s="7">
+        <v>4326</v>
+      </c>
+      <c r="P179" s="7">
+        <v>52</v>
+      </c>
+      <c r="Q179" s="7">
+        <v>238</v>
+      </c>
+      <c r="R179" s="7">
         <v>1075</v>
       </c>
     </row>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F90528-1007-6D4F-950E-BD8E8D74E648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF2CB56-EF3F-8843-BFB5-6A6563CE475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -865,6 +865,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1410,6 +1413,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>3042</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3349</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1990,6 +1996,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2535,6 +2544,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>4247</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4891</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3115,6 +3127,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3660,6 +3675,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>5393</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>6005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4240,6 +4258,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4785,6 +4806,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>3679</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3983</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5365,6 +5389,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5910,6 +5937,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>4877</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6490,6 +6520,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7035,6 +7068,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>6011</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>6389</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7617,6 +7653,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8162,6 +8201,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>2423</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>2582</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8744,6 +8786,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9289,6 +9334,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>5396</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>6389</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9871,6 +9919,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10416,6 +10467,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>4321</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10998,6 +11052,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11543,6 +11600,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>3274</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3262</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12125,6 +12185,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12670,6 +12733,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>4679</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4846</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13268,6 +13334,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13813,6 +13882,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14396,6 +14468,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -14941,6 +15016,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>227</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>223</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15524,6 +15602,9 @@
                 <c:pt idx="178">
                   <c:v>46181</c:v>
                 </c:pt>
+                <c:pt idx="179">
+                  <c:v>46188</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16069,6 +16150,9 @@
                 </c:pt>
                 <c:pt idx="178">
                   <c:v>1160</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16124,16 +16208,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="ko-KR"/>
@@ -16184,16 +16268,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="ko-KR"/>
@@ -16226,16 +16310,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="ko-KR"/>
@@ -16285,16 +16369,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="ko-KR"/>
@@ -16327,7 +16411,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1050">
+          <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -17236,7 +17323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S180"/>
+  <dimension ref="A1:S181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
@@ -27490,6 +27577,62 @@
       </c>
       <c r="R180" s="10">
         <v>1160</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18">
+      <c r="A181" s="7">
+        <v>46188</v>
+      </c>
+      <c r="B181" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C181" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E181" s="10">
+        <v>3349</v>
+      </c>
+      <c r="F181" s="10">
+        <v>4891</v>
+      </c>
+      <c r="G181" s="10">
+        <v>6005</v>
+      </c>
+      <c r="H181" s="10">
+        <v>3983</v>
+      </c>
+      <c r="I181" s="10">
+        <v>5254</v>
+      </c>
+      <c r="J181" s="10">
+        <v>6389</v>
+      </c>
+      <c r="K181" s="10">
+        <v>2582</v>
+      </c>
+      <c r="L181" s="10">
+        <v>6389</v>
+      </c>
+      <c r="M181" s="10">
+        <v>4785</v>
+      </c>
+      <c r="N181" s="10">
+        <v>3262</v>
+      </c>
+      <c r="O181" s="10">
+        <v>4846</v>
+      </c>
+      <c r="P181" s="10">
+        <v>54</v>
+      </c>
+      <c r="Q181" s="10">
+        <v>223</v>
+      </c>
+      <c r="R181" s="10">
+        <v>1154</v>
       </c>
     </row>
   </sheetData>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF2CB56-EF3F-8843-BFB5-6A6563CE475F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B91B0C-CED9-4BA3-9800-9CEAE07339A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="KCCI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -127,7 +127,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -259,9 +259,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -279,7 +279,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -868,6 +868,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1416,6 +1419,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>3349</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3747</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1999,6 +2005,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2547,6 +2556,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>4891</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3130,6 +3142,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3678,6 +3693,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>6005</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>6832</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4261,6 +4279,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4809,6 +4830,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>3983</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4566</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5392,6 +5416,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5940,6 +5967,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>5254</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5768</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6523,6 +6553,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7071,6 +7104,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>6389</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>6681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7656,6 +7692,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8204,6 +8243,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>2582</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>2813</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8789,6 +8831,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9337,6 +9382,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>6389</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>7320</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9922,6 +9970,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10470,6 +10521,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>4785</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5380</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11055,6 +11109,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11603,6 +11660,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>3262</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3394</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12188,6 +12248,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12736,6 +12799,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>4846</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13337,6 +13403,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13884,6 +13953,9 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="179">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="180">
                   <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
@@ -14471,6 +14543,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15019,6 +15094,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>223</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>214</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15605,6 +15683,9 @@
                 <c:pt idx="179">
                   <c:v>46188</c:v>
                 </c:pt>
+                <c:pt idx="180">
+                  <c:v>46195</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16153,6 +16234,9 @@
                 </c:pt>
                 <c:pt idx="179">
                   <c:v>1154</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1096</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17027,9 +17111,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -17067,7 +17151,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -17173,7 +17257,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -17315,7 +17399,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -17323,19 +17407,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <dimension ref="A1:S182"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="18" width="9.33203125" style="10" customWidth="1"/>
-    <col min="19" max="19" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.1640625" style="6"/>
+    <col min="1" max="1" width="10.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="7.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -17391,7 +17482,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>44872</v>
       </c>
@@ -17448,7 +17539,7 @@
       </c>
       <c r="S2" s="11"/>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>44879</v>
       </c>
@@ -17505,7 +17596,7 @@
       </c>
       <c r="S3" s="11"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>44886</v>
       </c>
@@ -17562,7 +17653,7 @@
       </c>
       <c r="S4" s="11"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>44893</v>
       </c>
@@ -17619,7 +17710,7 @@
       </c>
       <c r="S5" s="11"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="7">
         <v>44900</v>
       </c>
@@ -17676,7 +17767,7 @@
       </c>
       <c r="S6" s="11"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="7">
         <v>44907</v>
       </c>
@@ -17733,7 +17824,7 @@
       </c>
       <c r="S7" s="11"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="7">
         <v>44914</v>
       </c>
@@ -17790,7 +17881,7 @@
       </c>
       <c r="S8" s="11"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="7">
         <v>44921</v>
       </c>
@@ -17847,7 +17938,7 @@
       </c>
       <c r="S9" s="11"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>44928</v>
       </c>
@@ -17904,7 +17995,7 @@
       </c>
       <c r="S10" s="11"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>44935</v>
       </c>
@@ -17961,7 +18052,7 @@
       </c>
       <c r="S11" s="11"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="7">
         <v>44942</v>
       </c>
@@ -18018,7 +18109,7 @@
       </c>
       <c r="S12" s="11"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="7">
         <v>44951</v>
       </c>
@@ -18075,7 +18166,7 @@
       </c>
       <c r="S13" s="11"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="7">
         <v>44956</v>
       </c>
@@ -18132,7 +18223,7 @@
       </c>
       <c r="S14" s="11"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="7">
         <v>44963</v>
       </c>
@@ -18189,7 +18280,7 @@
       </c>
       <c r="S15" s="11"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="7">
         <v>44970</v>
       </c>
@@ -18246,7 +18337,7 @@
       </c>
       <c r="S16" s="11"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="7">
         <v>44977</v>
       </c>
@@ -18303,7 +18394,7 @@
       </c>
       <c r="S17" s="11"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="7">
         <v>44984</v>
       </c>
@@ -18360,7 +18451,7 @@
       </c>
       <c r="S18" s="11"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="7">
         <v>44991</v>
       </c>
@@ -18417,7 +18508,7 @@
       </c>
       <c r="S19" s="11"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="7">
         <v>44998</v>
       </c>
@@ -18474,7 +18565,7 @@
       </c>
       <c r="S20" s="11"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="7">
         <v>45005</v>
       </c>
@@ -18531,7 +18622,7 @@
       </c>
       <c r="S21" s="11"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="7">
         <v>45012</v>
       </c>
@@ -18588,7 +18679,7 @@
       </c>
       <c r="S22" s="11"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="7">
         <v>45019</v>
       </c>
@@ -18645,7 +18736,7 @@
       </c>
       <c r="S23" s="11"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="7">
         <v>45026</v>
       </c>
@@ -18702,7 +18793,7 @@
       </c>
       <c r="S24" s="11"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="7">
         <v>45033</v>
       </c>
@@ -18759,7 +18850,7 @@
       </c>
       <c r="S25" s="11"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="7">
         <v>45040</v>
       </c>
@@ -18816,7 +18907,7 @@
       </c>
       <c r="S26" s="11"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>45048</v>
       </c>
@@ -18873,7 +18964,7 @@
       </c>
       <c r="S27" s="11"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="7">
         <v>45054</v>
       </c>
@@ -18930,7 +19021,7 @@
       </c>
       <c r="S28" s="11"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="7">
         <v>45061</v>
       </c>
@@ -18987,7 +19078,7 @@
       </c>
       <c r="S29" s="11"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>45068</v>
       </c>
@@ -19044,7 +19135,7 @@
       </c>
       <c r="S30" s="11"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="7">
         <v>45076</v>
       </c>
@@ -19101,7 +19192,7 @@
       </c>
       <c r="S31" s="11"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="7">
         <v>45082</v>
       </c>
@@ -19158,7 +19249,7 @@
       </c>
       <c r="S32" s="11"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="7">
         <v>45089</v>
       </c>
@@ -19215,7 +19306,7 @@
       </c>
       <c r="S33" s="11"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="7">
         <v>45096</v>
       </c>
@@ -19272,7 +19363,7 @@
       </c>
       <c r="S34" s="11"/>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="7">
         <v>45103</v>
       </c>
@@ -19329,7 +19420,7 @@
       </c>
       <c r="S35" s="11"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="7">
         <v>45110</v>
       </c>
@@ -19386,7 +19477,7 @@
       </c>
       <c r="S36" s="11"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="7">
         <v>45117</v>
       </c>
@@ -19443,7 +19534,7 @@
       </c>
       <c r="S37" s="11"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>45124</v>
       </c>
@@ -19500,7 +19591,7 @@
       </c>
       <c r="S38" s="11"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="7">
         <v>45131</v>
       </c>
@@ -19557,7 +19648,7 @@
       </c>
       <c r="S39" s="11"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>45138</v>
       </c>
@@ -19614,7 +19705,7 @@
       </c>
       <c r="S40" s="11"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="7">
         <v>45145</v>
       </c>
@@ -19671,7 +19762,7 @@
       </c>
       <c r="S41" s="11"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="7">
         <v>45152</v>
       </c>
@@ -19728,7 +19819,7 @@
       </c>
       <c r="S42" s="11"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="7">
         <v>45159</v>
       </c>
@@ -19785,7 +19876,7 @@
       </c>
       <c r="S43" s="11"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="7">
         <v>45166</v>
       </c>
@@ -19842,7 +19933,7 @@
       </c>
       <c r="S44" s="11"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="7">
         <v>45173</v>
       </c>
@@ -19899,7 +19990,7 @@
       </c>
       <c r="S45" s="11"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="7">
         <v>45180</v>
       </c>
@@ -19956,7 +20047,7 @@
       </c>
       <c r="S46" s="11"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="7">
         <v>45187</v>
       </c>
@@ -20013,7 +20104,7 @@
       </c>
       <c r="S47" s="11"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="7">
         <v>45194</v>
       </c>
@@ -20070,7 +20161,7 @@
       </c>
       <c r="S48" s="11"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="7">
         <v>45209</v>
       </c>
@@ -20127,7 +20218,7 @@
       </c>
       <c r="S49" s="11"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" s="7">
         <v>45215</v>
       </c>
@@ -20184,7 +20275,7 @@
       </c>
       <c r="S50" s="11"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="7">
         <v>45222</v>
       </c>
@@ -20241,7 +20332,7 @@
       </c>
       <c r="S51" s="11"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" s="7">
         <v>45229</v>
       </c>
@@ -20298,7 +20389,7 @@
       </c>
       <c r="S52" s="11"/>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" s="7">
         <v>45236</v>
       </c>
@@ -20355,7 +20446,7 @@
       </c>
       <c r="S53" s="11"/>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" s="7">
         <v>45243</v>
       </c>
@@ -20412,7 +20503,7 @@
       </c>
       <c r="S54" s="11"/>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" s="7">
         <v>45250</v>
       </c>
@@ -20469,7 +20560,7 @@
       </c>
       <c r="S55" s="11"/>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" s="7">
         <v>45257</v>
       </c>
@@ -20526,7 +20617,7 @@
       </c>
       <c r="S56" s="11"/>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" s="7">
         <v>45264</v>
       </c>
@@ -20583,7 +20674,7 @@
       </c>
       <c r="S57" s="11"/>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" s="7">
         <v>45271</v>
       </c>
@@ -20640,7 +20731,7 @@
       </c>
       <c r="S58" s="11"/>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="7">
         <v>45278</v>
       </c>
@@ -20697,7 +20788,7 @@
       </c>
       <c r="S59" s="11"/>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="7">
         <v>45286</v>
       </c>
@@ -20754,7 +20845,7 @@
       </c>
       <c r="S60" s="11"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="7">
         <v>45293</v>
       </c>
@@ -20811,7 +20902,7 @@
       </c>
       <c r="S61" s="11"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="7">
         <v>45299</v>
       </c>
@@ -20868,7 +20959,7 @@
       </c>
       <c r="S62" s="11"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="7">
         <v>45306</v>
       </c>
@@ -20925,7 +21016,7 @@
       </c>
       <c r="S63" s="11"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
         <v>45313</v>
       </c>
@@ -20982,7 +21073,7 @@
       </c>
       <c r="S64" s="11"/>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="7">
         <v>45320</v>
       </c>
@@ -21039,7 +21130,7 @@
       </c>
       <c r="S65" s="11"/>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="7">
         <v>45327</v>
       </c>
@@ -21096,7 +21187,7 @@
       </c>
       <c r="S66" s="11"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="7">
         <v>45335</v>
       </c>
@@ -21153,7 +21244,7 @@
       </c>
       <c r="S67" s="11"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="7">
         <v>45341</v>
       </c>
@@ -21210,7 +21301,7 @@
       </c>
       <c r="S68" s="11"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="7">
         <v>45348</v>
       </c>
@@ -21267,7 +21358,7 @@
       </c>
       <c r="S69" s="11"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="7">
         <v>45355</v>
       </c>
@@ -21324,7 +21415,7 @@
       </c>
       <c r="S70" s="11"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="7">
         <v>45362</v>
       </c>
@@ -21381,7 +21472,7 @@
       </c>
       <c r="S71" s="11"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="7">
         <v>45369</v>
       </c>
@@ -21438,7 +21529,7 @@
       </c>
       <c r="S72" s="11"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" s="7">
         <v>45376</v>
       </c>
@@ -21495,7 +21586,7 @@
       </c>
       <c r="S73" s="11"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="7">
         <v>45383</v>
       </c>
@@ -21552,7 +21643,7 @@
       </c>
       <c r="S74" s="11"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="7">
         <v>45390</v>
       </c>
@@ -21609,7 +21700,7 @@
       </c>
       <c r="S75" s="11"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="7">
         <v>45397</v>
       </c>
@@ -21666,7 +21757,7 @@
       </c>
       <c r="S76" s="11"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>45404</v>
       </c>
@@ -21723,7 +21814,7 @@
       </c>
       <c r="S77" s="11"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
         <v>45411</v>
       </c>
@@ -21780,7 +21871,7 @@
       </c>
       <c r="S78" s="11"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="7">
         <v>45419</v>
       </c>
@@ -21837,7 +21928,7 @@
       </c>
       <c r="S79" s="11"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" s="7">
         <v>45425</v>
       </c>
@@ -21894,7 +21985,7 @@
       </c>
       <c r="S80" s="11"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>45432</v>
       </c>
@@ -21951,7 +22042,7 @@
       </c>
       <c r="S81" s="11"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" s="7">
         <v>45439</v>
       </c>
@@ -22008,7 +22099,7 @@
       </c>
       <c r="S82" s="11"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" s="7">
         <v>45446</v>
       </c>
@@ -22065,7 +22156,7 @@
       </c>
       <c r="S83" s="11"/>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" s="7">
         <v>45453</v>
       </c>
@@ -22122,7 +22213,7 @@
       </c>
       <c r="S84" s="11"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" s="7">
         <v>45460</v>
       </c>
@@ -22179,7 +22270,7 @@
       </c>
       <c r="S85" s="11"/>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" s="7">
         <v>45467</v>
       </c>
@@ -22236,7 +22327,7 @@
       </c>
       <c r="S86" s="11"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" s="7">
         <v>45474</v>
       </c>
@@ -22293,7 +22384,7 @@
       </c>
       <c r="S87" s="11"/>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" s="7">
         <v>45481</v>
       </c>
@@ -22350,7 +22441,7 @@
       </c>
       <c r="S88" s="11"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" s="7">
         <v>45488</v>
       </c>
@@ -22407,7 +22498,7 @@
       </c>
       <c r="S89" s="11"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" s="7">
         <v>45495</v>
       </c>
@@ -22464,7 +22555,7 @@
       </c>
       <c r="S90" s="11"/>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" s="7">
         <v>45502</v>
       </c>
@@ -22521,7 +22612,7 @@
       </c>
       <c r="S91" s="11"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" s="7">
         <v>45509</v>
       </c>
@@ -22578,7 +22669,7 @@
       </c>
       <c r="S92" s="11"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" s="7">
         <v>45516</v>
       </c>
@@ -22635,7 +22726,7 @@
       </c>
       <c r="S93" s="11"/>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" s="7">
         <v>45523</v>
       </c>
@@ -22692,7 +22783,7 @@
       </c>
       <c r="S94" s="11"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" s="7">
         <v>45530</v>
       </c>
@@ -22749,7 +22840,7 @@
       </c>
       <c r="S95" s="11"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" s="7">
         <v>45537</v>
       </c>
@@ -22806,7 +22897,7 @@
       </c>
       <c r="S96" s="11"/>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" s="7">
         <v>45544</v>
       </c>
@@ -22863,7 +22954,7 @@
       </c>
       <c r="S97" s="11"/>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" s="7">
         <v>45558</v>
       </c>
@@ -22920,7 +23011,7 @@
       </c>
       <c r="S98" s="11"/>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" s="7">
         <v>45565</v>
       </c>
@@ -22977,7 +23068,7 @@
       </c>
       <c r="S99" s="11"/>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" s="7">
         <v>45572</v>
       </c>
@@ -23034,7 +23125,7 @@
       </c>
       <c r="S100" s="11"/>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" s="7">
         <v>45579</v>
       </c>
@@ -23091,7 +23182,7 @@
       </c>
       <c r="S101" s="11"/>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" s="7">
         <v>45586</v>
       </c>
@@ -23148,7 +23239,7 @@
       </c>
       <c r="S102" s="11"/>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" s="7">
         <v>45593</v>
       </c>
@@ -23205,7 +23296,7 @@
       </c>
       <c r="S103" s="11"/>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" s="7">
         <v>45600</v>
       </c>
@@ -23262,7 +23353,7 @@
       </c>
       <c r="S104" s="11"/>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" s="7">
         <v>45607</v>
       </c>
@@ -23319,7 +23410,7 @@
       </c>
       <c r="S105" s="11"/>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" s="7">
         <v>45614</v>
       </c>
@@ -23376,7 +23467,7 @@
       </c>
       <c r="S106" s="11"/>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" s="7">
         <v>45621</v>
       </c>
@@ -23433,7 +23524,7 @@
       </c>
       <c r="S107" s="11"/>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" s="7">
         <v>45628</v>
       </c>
@@ -23490,7 +23581,7 @@
       </c>
       <c r="S108" s="11"/>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" s="7">
         <v>45635</v>
       </c>
@@ -23547,7 +23638,7 @@
       </c>
       <c r="S109" s="11"/>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" s="7">
         <v>45642</v>
       </c>
@@ -23604,7 +23695,7 @@
       </c>
       <c r="S110" s="11"/>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" s="7">
         <v>45649</v>
       </c>
@@ -23661,7 +23752,7 @@
       </c>
       <c r="S111" s="11"/>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" s="7">
         <v>45656</v>
       </c>
@@ -23718,7 +23809,7 @@
       </c>
       <c r="S112" s="11"/>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" s="7">
         <v>45663</v>
       </c>
@@ -23775,7 +23866,7 @@
       </c>
       <c r="S113" s="11"/>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" s="7">
         <v>45670</v>
       </c>
@@ -23832,7 +23923,7 @@
       </c>
       <c r="S114" s="11"/>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" s="7">
         <v>45677</v>
       </c>
@@ -23889,7 +23980,7 @@
       </c>
       <c r="S115" s="11"/>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" s="7">
         <v>45691</v>
       </c>
@@ -23946,7 +24037,7 @@
       </c>
       <c r="S116" s="11"/>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" s="7">
         <v>45698</v>
       </c>
@@ -24003,7 +24094,7 @@
       </c>
       <c r="S117" s="11"/>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" s="7">
         <v>45705</v>
       </c>
@@ -24060,7 +24151,7 @@
       </c>
       <c r="S118" s="11"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" s="7">
         <v>45712</v>
       </c>
@@ -24117,7 +24208,7 @@
       </c>
       <c r="S119" s="11"/>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" s="7">
         <v>45720</v>
       </c>
@@ -24174,7 +24265,7 @@
       </c>
       <c r="S120" s="11"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" s="7">
         <v>45726</v>
       </c>
@@ -24231,7 +24322,7 @@
       </c>
       <c r="S121" s="11"/>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" s="7">
         <v>45733</v>
       </c>
@@ -24288,7 +24379,7 @@
       </c>
       <c r="S122" s="11"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" s="7">
         <v>45740</v>
       </c>
@@ -24345,7 +24436,7 @@
       </c>
       <c r="S123" s="11"/>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
         <v>45747</v>
       </c>
@@ -24402,7 +24493,7 @@
       </c>
       <c r="S124" s="11"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" s="7">
         <v>45754</v>
       </c>
@@ -24459,7 +24550,7 @@
       </c>
       <c r="S125" s="11"/>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" s="7">
         <v>45761</v>
       </c>
@@ -24516,7 +24607,7 @@
       </c>
       <c r="S126" s="11"/>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127" s="7">
         <v>45768</v>
       </c>
@@ -24573,7 +24664,7 @@
       </c>
       <c r="S127" s="11"/>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128" s="7">
         <v>45775</v>
       </c>
@@ -24630,7 +24721,7 @@
       </c>
       <c r="S128" s="11"/>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" s="7">
         <v>45789</v>
       </c>
@@ -24687,7 +24778,7 @@
       </c>
       <c r="S129" s="11"/>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" s="7">
         <v>45796</v>
       </c>
@@ -24744,7 +24835,7 @@
       </c>
       <c r="S130" s="11"/>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" s="7">
         <v>45803</v>
       </c>
@@ -24801,7 +24892,7 @@
       </c>
       <c r="S131" s="11"/>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" s="7">
         <v>45810</v>
       </c>
@@ -24858,7 +24949,7 @@
       </c>
       <c r="S132" s="11"/>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" s="7">
         <v>45817</v>
       </c>
@@ -24915,7 +25006,7 @@
       </c>
       <c r="S133" s="11"/>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" s="7">
         <v>45824</v>
       </c>
@@ -24972,7 +25063,7 @@
       </c>
       <c r="S134" s="11"/>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" s="7">
         <v>45831</v>
       </c>
@@ -25029,7 +25120,7 @@
       </c>
       <c r="S135" s="11"/>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" s="7">
         <v>45838</v>
       </c>
@@ -25086,7 +25177,7 @@
       </c>
       <c r="S136" s="11"/>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" s="7">
         <v>45845</v>
       </c>
@@ -25143,7 +25234,7 @@
       </c>
       <c r="S137" s="11"/>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" s="7">
         <v>45852</v>
       </c>
@@ -25200,7 +25291,7 @@
       </c>
       <c r="S138" s="11"/>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" s="7">
         <v>45859</v>
       </c>
@@ -25257,7 +25348,7 @@
       </c>
       <c r="S139" s="11"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" s="7">
         <v>45866</v>
       </c>
@@ -25314,7 +25405,7 @@
       </c>
       <c r="S140" s="11"/>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" s="7">
         <v>45873</v>
       </c>
@@ -25371,7 +25462,7 @@
       </c>
       <c r="S141" s="11"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142" s="7">
         <v>45880</v>
       </c>
@@ -25428,7 +25519,7 @@
       </c>
       <c r="S142" s="11"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" s="7">
         <v>45887</v>
       </c>
@@ -25485,7 +25576,7 @@
       </c>
       <c r="S143" s="11"/>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144" s="7">
         <v>45894</v>
       </c>
@@ -25542,7 +25633,7 @@
       </c>
       <c r="S144" s="11"/>
     </row>
-    <row r="145" spans="1:19">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145" s="7">
         <v>45901</v>
       </c>
@@ -25599,7 +25690,7 @@
       </c>
       <c r="S145" s="11"/>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146" s="7">
         <v>45908</v>
       </c>
@@ -25656,7 +25747,7 @@
       </c>
       <c r="S146" s="11"/>
     </row>
-    <row r="147" spans="1:19">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147" s="7">
         <v>45915</v>
       </c>
@@ -25713,7 +25804,7 @@
       </c>
       <c r="S147" s="11"/>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148" s="7">
         <v>45922</v>
       </c>
@@ -25770,7 +25861,7 @@
       </c>
       <c r="S148" s="11"/>
     </row>
-    <row r="149" spans="1:19">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149" s="7">
         <v>45929</v>
       </c>
@@ -25827,7 +25918,7 @@
       </c>
       <c r="S149" s="11"/>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150" s="7">
         <v>45950</v>
       </c>
@@ -25884,7 +25975,7 @@
       </c>
       <c r="S150" s="11"/>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151" s="7">
         <v>45957</v>
       </c>
@@ -25941,7 +26032,7 @@
       </c>
       <c r="S151" s="11"/>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152" s="7">
         <v>45964</v>
       </c>
@@ -25998,7 +26089,7 @@
       </c>
       <c r="S152" s="11"/>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153" s="7">
         <v>45971</v>
       </c>
@@ -26055,7 +26146,7 @@
       </c>
       <c r="S153" s="11"/>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154" s="7">
         <v>45978</v>
       </c>
@@ -26112,7 +26203,7 @@
       </c>
       <c r="S154" s="11"/>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155" s="7">
         <v>45985</v>
       </c>
@@ -26169,7 +26260,7 @@
       </c>
       <c r="S155" s="11"/>
     </row>
-    <row r="156" spans="1:19">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156" s="7">
         <v>45992</v>
       </c>
@@ -26226,7 +26317,7 @@
       </c>
       <c r="S156" s="11"/>
     </row>
-    <row r="157" spans="1:19">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157" s="7">
         <v>45999</v>
       </c>
@@ -26283,7 +26374,7 @@
       </c>
       <c r="S157" s="11"/>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158" s="7">
         <v>46006</v>
       </c>
@@ -26340,7 +26431,7 @@
       </c>
       <c r="S158" s="11"/>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A159" s="7">
         <v>46013</v>
       </c>
@@ -26397,7 +26488,7 @@
       </c>
       <c r="S159" s="11"/>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160" s="7">
         <v>46020</v>
       </c>
@@ -26454,7 +26545,7 @@
       </c>
       <c r="S160" s="11"/>
     </row>
-    <row r="161" spans="1:19">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161" s="7">
         <v>46034</v>
       </c>
@@ -26511,7 +26602,7 @@
       </c>
       <c r="S161" s="11"/>
     </row>
-    <row r="162" spans="1:19">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A162" s="7">
         <v>46041</v>
       </c>
@@ -26568,7 +26659,7 @@
       </c>
       <c r="S162" s="11"/>
     </row>
-    <row r="163" spans="1:19">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A163" s="7">
         <v>46048</v>
       </c>
@@ -26625,7 +26716,7 @@
       </c>
       <c r="S163" s="11"/>
     </row>
-    <row r="164" spans="1:19">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A164" s="7">
         <v>46055</v>
       </c>
@@ -26682,7 +26773,7 @@
       </c>
       <c r="S164" s="11"/>
     </row>
-    <row r="165" spans="1:19">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A165" s="7">
         <v>46062</v>
       </c>
@@ -26739,7 +26830,7 @@
       </c>
       <c r="S165" s="11"/>
     </row>
-    <row r="166" spans="1:19">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A166" s="7">
         <v>46076</v>
       </c>
@@ -26795,7 +26886,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="167" spans="1:19">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A167" s="7">
         <v>46084</v>
       </c>
@@ -26851,7 +26942,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="168" spans="1:19">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A168" s="7">
         <v>46090</v>
       </c>
@@ -26907,7 +26998,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="169" spans="1:19">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A169" s="7">
         <v>46097</v>
       </c>
@@ -26963,7 +27054,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="170" spans="1:19">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A170" s="7">
         <v>46104</v>
       </c>
@@ -27019,7 +27110,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="171" spans="1:19">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A171" s="7">
         <v>46111</v>
       </c>
@@ -27075,7 +27166,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="172" spans="1:19">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A172" s="7">
         <v>46118</v>
       </c>
@@ -27131,7 +27222,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="173" spans="1:19">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A173" s="7">
         <v>46125</v>
       </c>
@@ -27187,7 +27278,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="174" spans="1:19">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A174" s="7">
         <v>46132</v>
       </c>
@@ -27243,7 +27334,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="175" spans="1:19">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A175" s="7">
         <v>46139</v>
       </c>
@@ -27299,7 +27390,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="176" spans="1:19">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A176" s="7">
         <v>46153</v>
       </c>
@@ -27355,7 +27446,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A177" s="7">
         <v>46160</v>
       </c>
@@ -27411,7 +27502,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A178" s="7">
         <v>46168</v>
       </c>
@@ -27467,7 +27558,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="179" spans="1:18">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A179" s="7">
         <v>46174</v>
       </c>
@@ -27523,7 +27614,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="180" spans="1:18">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A180" s="7">
         <v>46181</v>
       </c>
@@ -27579,7 +27670,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A181" s="7">
         <v>46188</v>
       </c>
@@ -27633,6 +27724,62 @@
       </c>
       <c r="R181" s="10">
         <v>1154</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A182" s="7">
+        <v>46195</v>
+      </c>
+      <c r="B182" s="7">
+        <v>46195</v>
+      </c>
+      <c r="C182" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D182" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E182" s="10">
+        <v>3747</v>
+      </c>
+      <c r="F182" s="10">
+        <v>5729</v>
+      </c>
+      <c r="G182" s="10">
+        <v>6832</v>
+      </c>
+      <c r="H182" s="10">
+        <v>4566</v>
+      </c>
+      <c r="I182" s="10">
+        <v>5768</v>
+      </c>
+      <c r="J182" s="10">
+        <v>6681</v>
+      </c>
+      <c r="K182" s="10">
+        <v>2813</v>
+      </c>
+      <c r="L182" s="10">
+        <v>7320</v>
+      </c>
+      <c r="M182" s="10">
+        <v>5380</v>
+      </c>
+      <c r="N182" s="10">
+        <v>3394</v>
+      </c>
+      <c r="O182" s="10">
+        <v>5045</v>
+      </c>
+      <c r="P182" s="10">
+        <v>54</v>
+      </c>
+      <c r="Q182" s="10">
+        <v>214</v>
+      </c>
+      <c r="R182" s="10">
+        <v>1096</v>
       </c>
     </row>
   </sheetData>
@@ -27648,14 +27795,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EF7E42-3273-4C27-80E3-741AD2FB330F}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="6"/>
-    <col min="2" max="2" width="12.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.1640625" style="6"/>
+    <col min="1" max="1" width="9.109375" style="6"/>
+    <col min="2" max="2" width="12.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="12" t="s">
         <v>19</v>
       </c>
@@ -27663,7 +27810,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="12" t="s">
         <v>20</v>
       </c>
@@ -27684,9 +27831,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38BD5038-94A8-4C07-9E87-4FDF24EEDBD6}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="16384" width="9.1640625" style="1"/>
+    <col min="1" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/freight/KOBC Container Composite Index.xlsx
+++ b/data/freight/KOBC Container Composite Index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B91B0C-CED9-4BA3-9800-9CEAE07339A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB54D413-8AED-49EA-B2FA-99E5854499E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{60D533B4-BABA-4A3A-BA77-90631A7D5AF4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="24">
   <si>
     <t>KCCI</t>
   </si>
@@ -871,6 +871,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1422,6 +1425,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>3747</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3920</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2008,6 +2014,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2559,6 +2568,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>5729</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5969</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3145,6 +3157,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3696,6 +3711,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>6832</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>7217</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4282,6 +4300,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4833,6 +4854,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>4566</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4720</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5419,6 +5443,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -5970,6 +5997,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>5768</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5876</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6556,6 +6586,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7107,6 +7140,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>6681</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>6783</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7695,6 +7731,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -8246,6 +8285,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>2813</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3096</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8834,6 +8876,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -9385,6 +9430,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>7320</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>7854</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9973,6 +10021,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10524,6 +10575,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>5380</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5840</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11112,6 +11166,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -11663,6 +11720,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>3394</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3483</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12251,6 +12311,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -12802,6 +12865,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>5045</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>5260</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13406,6 +13472,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13956,6 +14025,9 @@
                   <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="180">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="181">
                   <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
@@ -14546,6 +14618,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -15097,6 +15172,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>214</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>222</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15686,6 +15764,9 @@
                 <c:pt idx="180">
                   <c:v>46195</c:v>
                 </c:pt>
+                <c:pt idx="181">
+                  <c:v>46202</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -16237,6 +16318,9 @@
                 </c:pt>
                 <c:pt idx="180">
                   <c:v>1096</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1098</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17407,7 +17491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DA357B4-D493-460A-8A01-15E726FCB459}">
-  <dimension ref="A1:S182"/>
+  <dimension ref="A1:S183"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.77734375" style="7" bestFit="1" customWidth="1"/>
@@ -27780,6 +27864,62 @@
       </c>
       <c r="R182" s="10">
         <v>1096</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A183" s="7">
+        <v>46202</v>
+      </c>
+      <c r="B183" s="7">
+        <v>46202</v>
+      </c>
+      <c r="C183" s="8">
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D183" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E183" s="10">
+        <v>3920</v>
+      </c>
+      <c r="F183" s="10">
+        <v>5969</v>
+      </c>
+      <c r="G183" s="10">
+        <v>7217</v>
+      </c>
+      <c r="H183" s="10">
+        <v>4720</v>
+      </c>
+      <c r="I183" s="10">
+        <v>5876</v>
+      </c>
+      <c r="J183" s="10">
+        <v>6783</v>
+      </c>
+      <c r="K183" s="10">
+        <v>3096</v>
+      </c>
+      <c r="L183" s="10">
+        <v>7854</v>
+      </c>
+      <c r="M183" s="10">
+        <v>5840</v>
+      </c>
+      <c r="N183" s="10">
+        <v>3483</v>
+      </c>
+      <c r="O183" s="10">
+        <v>5260</v>
+      </c>
+      <c r="P183" s="10">
+        <v>54</v>
+      </c>
+      <c r="Q183" s="10">
+        <v>222</v>
+      </c>
+      <c r="R183" s="10">
+        <v>1098</v>
       </c>
     </row>
   </sheetData>
